--- a/SQL_CIS2/MD_RIND_1058.xlsx
+++ b/SQL_CIS2/MD_RIND_1058.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212">
   <si>
     <t>ID_MD</t>
   </si>
@@ -1757,6 +1757,10 @@
   </si>
   <si>
     <t>322.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bibliotecar/bibliotecară
+</t>
   </si>
   <si>
     <t>411.1.1</t>
@@ -21043,7 +21047,7 @@
     </row>
     <row r="388" ht="15">
       <c r="A388" s="1">
-        <v>120447</v>
+        <v>120591</v>
       </c>
       <c r="B388" s="1">
         <v>50</v>
@@ -21064,7 +21068,7 @@
         <v>2015</v>
       </c>
       <c r="H388" s="4" t="s">
-        <v>73</v>
+        <v>581</v>
       </c>
       <c r="I388" s="4" t="s">
         <v>16</v>
@@ -21102,7 +21106,7 @@
         <v>2015</v>
       </c>
       <c r="F389" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G389" s="1">
         <v>2015</v>
@@ -21146,7 +21150,7 @@
         <v>2015</v>
       </c>
       <c r="F390" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G390" s="1">
         <v>2015</v>
@@ -21190,7 +21194,7 @@
         <v>2015</v>
       </c>
       <c r="F391" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G391" s="1">
         <v>2015</v>
@@ -21234,7 +21238,7 @@
         <v>2015</v>
       </c>
       <c r="F392" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G392" s="1">
         <v>2015</v>
@@ -21278,7 +21282,7 @@
         <v>2015</v>
       </c>
       <c r="F393" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G393" s="1">
         <v>2015</v>
@@ -21322,7 +21326,7 @@
         <v>2015</v>
       </c>
       <c r="F394" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G394" s="1">
         <v>2015</v>
@@ -21366,7 +21370,7 @@
         <v>2015</v>
       </c>
       <c r="F395" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G395" s="1">
         <v>2015</v>
@@ -21410,7 +21414,7 @@
         <v>2015</v>
       </c>
       <c r="F396" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G396" s="1">
         <v>2015</v>
@@ -21454,7 +21458,7 @@
         <v>2015</v>
       </c>
       <c r="F397" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G397" s="1">
         <v>2015</v>
@@ -21498,7 +21502,7 @@
         <v>2015</v>
       </c>
       <c r="F398" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G398" s="1">
         <v>2015</v>
@@ -21542,7 +21546,7 @@
         <v>2015</v>
       </c>
       <c r="F399" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G399" s="1">
         <v>2015</v>
@@ -21586,7 +21590,7 @@
         <v>2015</v>
       </c>
       <c r="F400" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G400" s="1">
         <v>2015</v>
@@ -21630,7 +21634,7 @@
         <v>2015</v>
       </c>
       <c r="F401" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G401" s="1">
         <v>2015</v>
@@ -21674,7 +21678,7 @@
         <v>2015</v>
       </c>
       <c r="F402" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G402" s="1">
         <v>2015</v>
@@ -21718,7 +21722,7 @@
         <v>2015</v>
       </c>
       <c r="F403" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G403" s="1">
         <v>2015</v>
@@ -21762,7 +21766,7 @@
         <v>2015</v>
       </c>
       <c r="F404" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G404" s="1">
         <v>2015</v>
@@ -21806,7 +21810,7 @@
         <v>2015</v>
       </c>
       <c r="F405" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G405" s="1">
         <v>2015</v>
@@ -21850,7 +21854,7 @@
         <v>2015</v>
       </c>
       <c r="F406" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G406" s="1">
         <v>2015</v>
@@ -21894,7 +21898,7 @@
         <v>2015</v>
       </c>
       <c r="F407" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G407" s="1">
         <v>2015</v>
@@ -21938,7 +21942,7 @@
         <v>2015</v>
       </c>
       <c r="F408" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G408" s="1">
         <v>2015</v>
@@ -21982,7 +21986,7 @@
         <v>2015</v>
       </c>
       <c r="F409" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G409" s="1">
         <v>2015</v>
@@ -22026,7 +22030,7 @@
         <v>2015</v>
       </c>
       <c r="F410" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G410" s="1">
         <v>2015</v>
@@ -22070,7 +22074,7 @@
         <v>2015</v>
       </c>
       <c r="F411" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G411" s="1">
         <v>2015</v>
@@ -22114,7 +22118,7 @@
         <v>2015</v>
       </c>
       <c r="F412" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G412" s="1">
         <v>2015</v>
@@ -22158,7 +22162,7 @@
         <v>2015</v>
       </c>
       <c r="F413" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G413" s="1">
         <v>2015</v>
@@ -22202,7 +22206,7 @@
         <v>2015</v>
       </c>
       <c r="F414" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G414" s="1">
         <v>2015</v>
@@ -22246,7 +22250,7 @@
         <v>2015</v>
       </c>
       <c r="F415" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G415" s="1">
         <v>2015</v>
@@ -22290,7 +22294,7 @@
         <v>2015</v>
       </c>
       <c r="F416" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G416" s="1">
         <v>2015</v>
@@ -22334,7 +22338,7 @@
         <v>2015</v>
       </c>
       <c r="F417" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G417" s="1">
         <v>2015</v>
@@ -22378,7 +22382,7 @@
         <v>2015</v>
       </c>
       <c r="F418" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G418" s="1">
         <v>2015</v>
@@ -22422,7 +22426,7 @@
         <v>2015</v>
       </c>
       <c r="F419" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G419" s="1">
         <v>2015</v>
@@ -22466,7 +22470,7 @@
         <v>2015</v>
       </c>
       <c r="F420" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G420" s="1">
         <v>2015</v>
@@ -22510,7 +22514,7 @@
         <v>2015</v>
       </c>
       <c r="F421" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G421" s="1">
         <v>2015</v>
@@ -22554,7 +22558,7 @@
         <v>2015</v>
       </c>
       <c r="F422" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G422" s="1">
         <v>2015</v>
@@ -22598,7 +22602,7 @@
         <v>2015</v>
       </c>
       <c r="F423" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G423" s="1">
         <v>2015</v>
@@ -22642,7 +22646,7 @@
         <v>2015</v>
       </c>
       <c r="F424" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G424" s="1">
         <v>2015</v>
@@ -22686,7 +22690,7 @@
         <v>2015</v>
       </c>
       <c r="F425" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G425" s="1">
         <v>2015</v>
@@ -22730,7 +22734,7 @@
         <v>2015</v>
       </c>
       <c r="F426" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G426" s="1">
         <v>2015</v>
@@ -22774,7 +22778,7 @@
         <v>2015</v>
       </c>
       <c r="F427" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G427" s="1">
         <v>2015</v>
@@ -22818,7 +22822,7 @@
         <v>2015</v>
       </c>
       <c r="F428" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G428" s="1">
         <v>2015</v>
@@ -22862,7 +22866,7 @@
         <v>2015</v>
       </c>
       <c r="F429" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G429" s="1">
         <v>2015</v>
@@ -22906,7 +22910,7 @@
         <v>2015</v>
       </c>
       <c r="F430" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G430" s="1">
         <v>2015</v>
@@ -22950,7 +22954,7 @@
         <v>2015</v>
       </c>
       <c r="F431" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G431" s="1">
         <v>2015</v>
@@ -22994,7 +22998,7 @@
         <v>2015</v>
       </c>
       <c r="F432" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G432" s="1">
         <v>2015</v>
@@ -23038,7 +23042,7 @@
         <v>2015</v>
       </c>
       <c r="F433" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G433" s="1">
         <v>2015</v>
@@ -23082,7 +23086,7 @@
         <v>2015</v>
       </c>
       <c r="F434" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G434" s="1">
         <v>2015</v>
@@ -23126,7 +23130,7 @@
         <v>2015</v>
       </c>
       <c r="F435" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G435" s="1">
         <v>2015</v>
@@ -23170,7 +23174,7 @@
         <v>2015</v>
       </c>
       <c r="F436" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G436" s="1">
         <v>2015</v>
@@ -23214,7 +23218,7 @@
         <v>2015</v>
       </c>
       <c r="F437" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G437" s="1">
         <v>2015</v>
@@ -23258,7 +23262,7 @@
         <v>2015</v>
       </c>
       <c r="F438" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G438" s="1">
         <v>2015</v>
@@ -23302,7 +23306,7 @@
         <v>2015</v>
       </c>
       <c r="F439" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G439" s="1">
         <v>2015</v>
@@ -23346,7 +23350,7 @@
         <v>2015</v>
       </c>
       <c r="F440" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G440" s="1">
         <v>2015</v>
@@ -23390,7 +23394,7 @@
         <v>2015</v>
       </c>
       <c r="F441" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G441" s="1">
         <v>2015</v>
@@ -23434,7 +23438,7 @@
         <v>2015</v>
       </c>
       <c r="F442" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G442" s="1">
         <v>2015</v>
@@ -23478,7 +23482,7 @@
         <v>2015</v>
       </c>
       <c r="F443" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G443" s="1">
         <v>2015</v>
@@ -23522,7 +23526,7 @@
         <v>2015</v>
       </c>
       <c r="F444" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G444" s="1">
         <v>2015</v>
@@ -23566,7 +23570,7 @@
         <v>2015</v>
       </c>
       <c r="F445" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G445" s="1">
         <v>2015</v>
@@ -23610,7 +23614,7 @@
         <v>2015</v>
       </c>
       <c r="F446" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G446" s="1">
         <v>2015</v>
@@ -23654,7 +23658,7 @@
         <v>2015</v>
       </c>
       <c r="F447" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G447" s="1">
         <v>2015</v>
@@ -23698,7 +23702,7 @@
         <v>2015</v>
       </c>
       <c r="F448" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G448" s="1">
         <v>2015</v>
@@ -23742,7 +23746,7 @@
         <v>2015</v>
       </c>
       <c r="F449" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G449" s="1">
         <v>2015</v>
@@ -23786,7 +23790,7 @@
         <v>2015</v>
       </c>
       <c r="F450" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G450" s="1">
         <v>2015</v>
@@ -23830,7 +23834,7 @@
         <v>2015</v>
       </c>
       <c r="F451" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G451" s="1">
         <v>2015</v>
@@ -23874,7 +23878,7 @@
         <v>2015</v>
       </c>
       <c r="F452" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G452" s="1">
         <v>2015</v>
@@ -23918,7 +23922,7 @@
         <v>2015</v>
       </c>
       <c r="F453" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G453" s="1">
         <v>2015</v>
@@ -23962,7 +23966,7 @@
         <v>2015</v>
       </c>
       <c r="F454" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G454" s="1">
         <v>2015</v>
@@ -24006,7 +24010,7 @@
         <v>2015</v>
       </c>
       <c r="F455" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G455" s="1">
         <v>2015</v>
@@ -24050,7 +24054,7 @@
         <v>2015</v>
       </c>
       <c r="F456" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G456" s="1">
         <v>2015</v>
@@ -24094,7 +24098,7 @@
         <v>2015</v>
       </c>
       <c r="F457" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G457" s="1">
         <v>2015</v>
@@ -24138,7 +24142,7 @@
         <v>2015</v>
       </c>
       <c r="F458" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G458" s="1">
         <v>2015</v>
@@ -24182,7 +24186,7 @@
         <v>2015</v>
       </c>
       <c r="F459" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G459" s="1">
         <v>2015</v>
@@ -24226,7 +24230,7 @@
         <v>2015</v>
       </c>
       <c r="F460" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G460" s="1">
         <v>2015</v>
@@ -24270,7 +24274,7 @@
         <v>2015</v>
       </c>
       <c r="F461" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G461" s="1">
         <v>2015</v>
@@ -24314,7 +24318,7 @@
         <v>2015</v>
       </c>
       <c r="F462" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G462" s="1">
         <v>2015</v>
@@ -24358,7 +24362,7 @@
         <v>2015</v>
       </c>
       <c r="F463" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G463" s="1">
         <v>2015</v>
@@ -24402,7 +24406,7 @@
         <v>2015</v>
       </c>
       <c r="F464" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G464" s="1">
         <v>2015</v>
@@ -24446,7 +24450,7 @@
         <v>2015</v>
       </c>
       <c r="F465" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G465" s="1">
         <v>2015</v>
@@ -24490,7 +24494,7 @@
         <v>2015</v>
       </c>
       <c r="F466" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G466" s="1">
         <v>2015</v>
@@ -24534,7 +24538,7 @@
         <v>2015</v>
       </c>
       <c r="F467" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G467" s="1">
         <v>2015</v>
@@ -24578,7 +24582,7 @@
         <v>2015</v>
       </c>
       <c r="F468" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G468" s="1">
         <v>2015</v>
@@ -24622,7 +24626,7 @@
         <v>2015</v>
       </c>
       <c r="F469" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G469" s="1">
         <v>2015</v>
@@ -24666,7 +24670,7 @@
         <v>2015</v>
       </c>
       <c r="F470" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G470" s="1">
         <v>2015</v>
@@ -24710,7 +24714,7 @@
         <v>2015</v>
       </c>
       <c r="F471" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G471" s="1">
         <v>2015</v>
@@ -24754,7 +24758,7 @@
         <v>2015</v>
       </c>
       <c r="F472" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G472" s="1">
         <v>2015</v>
@@ -24798,7 +24802,7 @@
         <v>2015</v>
       </c>
       <c r="F473" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G473" s="1">
         <v>2015</v>
@@ -24842,7 +24846,7 @@
         <v>2015</v>
       </c>
       <c r="F474" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G474" s="1">
         <v>2015</v>
@@ -24886,7 +24890,7 @@
         <v>2015</v>
       </c>
       <c r="F475" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G475" s="1">
         <v>2015</v>
@@ -24930,7 +24934,7 @@
         <v>2015</v>
       </c>
       <c r="F476" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G476" s="1">
         <v>2015</v>
@@ -24974,7 +24978,7 @@
         <v>2015</v>
       </c>
       <c r="F477" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="G477" s="1">
         <v>2015</v>
@@ -25018,7 +25022,7 @@
         <v>2015</v>
       </c>
       <c r="F478" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G478" s="1">
         <v>2015</v>
@@ -25062,7 +25066,7 @@
         <v>2015</v>
       </c>
       <c r="F479" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G479" s="1">
         <v>2015</v>
@@ -25106,7 +25110,7 @@
         <v>2015</v>
       </c>
       <c r="F480" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G480" s="1">
         <v>2015</v>
@@ -25150,7 +25154,7 @@
         <v>2015</v>
       </c>
       <c r="F481" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G481" s="1">
         <v>2015</v>
@@ -25194,7 +25198,7 @@
         <v>2015</v>
       </c>
       <c r="F482" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G482" s="1">
         <v>2015</v>
@@ -25238,7 +25242,7 @@
         <v>2015</v>
       </c>
       <c r="F483" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G483" s="1">
         <v>2015</v>
@@ -25282,7 +25286,7 @@
         <v>2015</v>
       </c>
       <c r="F484" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G484" s="1">
         <v>2015</v>
@@ -25326,7 +25330,7 @@
         <v>2015</v>
       </c>
       <c r="F485" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G485" s="1">
         <v>2015</v>
@@ -25370,7 +25374,7 @@
         <v>2015</v>
       </c>
       <c r="F486" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G486" s="1">
         <v>2015</v>
@@ -25414,7 +25418,7 @@
         <v>2015</v>
       </c>
       <c r="F487" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G487" s="1">
         <v>2015</v>
@@ -25458,7 +25462,7 @@
         <v>2015</v>
       </c>
       <c r="F488" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G488" s="1">
         <v>2015</v>
@@ -25502,7 +25506,7 @@
         <v>2015</v>
       </c>
       <c r="F489" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G489" s="1">
         <v>2015</v>
@@ -25546,7 +25550,7 @@
         <v>2015</v>
       </c>
       <c r="F490" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G490" s="1">
         <v>2015</v>
@@ -25590,7 +25594,7 @@
         <v>2015</v>
       </c>
       <c r="F491" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G491" s="1">
         <v>2015</v>
@@ -25634,7 +25638,7 @@
         <v>2015</v>
       </c>
       <c r="F492" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G492" s="1">
         <v>2015</v>
@@ -25678,7 +25682,7 @@
         <v>2015</v>
       </c>
       <c r="F493" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G493" s="1">
         <v>2015</v>
@@ -25722,7 +25726,7 @@
         <v>2015</v>
       </c>
       <c r="F494" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G494" s="1">
         <v>2015</v>
@@ -25766,7 +25770,7 @@
         <v>2015</v>
       </c>
       <c r="F495" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G495" s="1">
         <v>2015</v>
@@ -25810,7 +25814,7 @@
         <v>2015</v>
       </c>
       <c r="F496" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G496" s="1">
         <v>2015</v>
@@ -25854,7 +25858,7 @@
         <v>2015</v>
       </c>
       <c r="F497" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G497" s="1">
         <v>2015</v>
@@ -25898,7 +25902,7 @@
         <v>2015</v>
       </c>
       <c r="F498" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G498" s="1">
         <v>2015</v>
@@ -25942,7 +25946,7 @@
         <v>2015</v>
       </c>
       <c r="F499" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G499" s="1">
         <v>2015</v>
@@ -25986,7 +25990,7 @@
         <v>2015</v>
       </c>
       <c r="F500" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G500" s="1">
         <v>2015</v>
@@ -26030,7 +26034,7 @@
         <v>2015</v>
       </c>
       <c r="F501" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G501" s="1">
         <v>2015</v>
@@ -26074,7 +26078,7 @@
         <v>2015</v>
       </c>
       <c r="F502" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G502" s="1">
         <v>2015</v>
@@ -26118,7 +26122,7 @@
         <v>2015</v>
       </c>
       <c r="F503" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G503" s="1">
         <v>2015</v>
@@ -26162,7 +26166,7 @@
         <v>2015</v>
       </c>
       <c r="F504" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G504" s="1">
         <v>2015</v>
@@ -26206,7 +26210,7 @@
         <v>2015</v>
       </c>
       <c r="F505" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G505" s="1">
         <v>2015</v>
@@ -26250,7 +26254,7 @@
         <v>2015</v>
       </c>
       <c r="F506" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G506" s="1">
         <v>2015</v>
@@ -26294,7 +26298,7 @@
         <v>2015</v>
       </c>
       <c r="F507" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G507" s="1">
         <v>2015</v>
@@ -26338,7 +26342,7 @@
         <v>2015</v>
       </c>
       <c r="F508" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G508" s="1">
         <v>2015</v>
@@ -26382,7 +26386,7 @@
         <v>2015</v>
       </c>
       <c r="F509" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G509" s="1">
         <v>2015</v>
@@ -26426,7 +26430,7 @@
         <v>2015</v>
       </c>
       <c r="F510" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G510" s="1">
         <v>2015</v>
@@ -26470,7 +26474,7 @@
         <v>2015</v>
       </c>
       <c r="F511" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G511" s="1">
         <v>2015</v>
@@ -26514,7 +26518,7 @@
         <v>2015</v>
       </c>
       <c r="F512" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G512" s="1">
         <v>2015</v>
@@ -26558,7 +26562,7 @@
         <v>2015</v>
       </c>
       <c r="F513" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G513" s="1">
         <v>2015</v>
@@ -26602,7 +26606,7 @@
         <v>2015</v>
       </c>
       <c r="F514" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G514" s="1">
         <v>2015</v>
@@ -26646,7 +26650,7 @@
         <v>2015</v>
       </c>
       <c r="F515" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G515" s="1">
         <v>2015</v>
@@ -26690,7 +26694,7 @@
         <v>2015</v>
       </c>
       <c r="F516" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G516" s="1">
         <v>2015</v>
@@ -26734,7 +26738,7 @@
         <v>2015</v>
       </c>
       <c r="F517" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G517" s="1">
         <v>2015</v>
@@ -26778,7 +26782,7 @@
         <v>2015</v>
       </c>
       <c r="F518" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G518" s="1">
         <v>2015</v>
@@ -26822,7 +26826,7 @@
         <v>2015</v>
       </c>
       <c r="F519" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G519" s="1">
         <v>2015</v>
@@ -26866,7 +26870,7 @@
         <v>2015</v>
       </c>
       <c r="F520" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G520" s="1">
         <v>2015</v>
@@ -26910,7 +26914,7 @@
         <v>2015</v>
       </c>
       <c r="F521" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G521" s="1">
         <v>2015</v>
@@ -26954,7 +26958,7 @@
         <v>2015</v>
       </c>
       <c r="F522" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G522" s="1">
         <v>2015</v>
@@ -26998,7 +27002,7 @@
         <v>2015</v>
       </c>
       <c r="F523" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G523" s="1">
         <v>2015</v>
@@ -27042,7 +27046,7 @@
         <v>2015</v>
       </c>
       <c r="F524" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G524" s="1">
         <v>2015</v>
@@ -27086,7 +27090,7 @@
         <v>2015</v>
       </c>
       <c r="F525" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G525" s="1">
         <v>2015</v>
@@ -27130,7 +27134,7 @@
         <v>2015</v>
       </c>
       <c r="F526" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G526" s="1">
         <v>2015</v>
@@ -27174,7 +27178,7 @@
         <v>2015</v>
       </c>
       <c r="F527" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G527" s="1">
         <v>2015</v>
@@ -27218,7 +27222,7 @@
         <v>2015</v>
       </c>
       <c r="F528" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G528" s="1">
         <v>2015</v>
@@ -27262,7 +27266,7 @@
         <v>2015</v>
       </c>
       <c r="F529" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G529" s="1">
         <v>2015</v>
@@ -27306,7 +27310,7 @@
         <v>2015</v>
       </c>
       <c r="F530" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G530" s="1">
         <v>2015</v>
@@ -27350,13 +27354,13 @@
         <v>2015</v>
       </c>
       <c r="F531" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G531" s="1">
         <v>2015</v>
       </c>
       <c r="H531" s="4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I531" s="4" t="s">
         <v>16</v>
@@ -27392,13 +27396,13 @@
         <v>2015</v>
       </c>
       <c r="F532" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G532" s="1">
         <v>2015</v>
       </c>
       <c r="H532" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I532" s="4" t="s">
         <v>16</v>
@@ -27434,13 +27438,13 @@
         <v>2015</v>
       </c>
       <c r="F533" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G533" s="1">
         <v>2015</v>
       </c>
       <c r="H533" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I533" s="4" t="s">
         <v>16</v>
@@ -27478,13 +27482,13 @@
         <v>2015</v>
       </c>
       <c r="F534" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G534" s="1">
         <v>2015</v>
       </c>
       <c r="H534" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="I534" s="4" t="s">
         <v>16</v>
@@ -27522,13 +27526,13 @@
         <v>2015</v>
       </c>
       <c r="F535" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G535" s="1">
         <v>2015</v>
       </c>
       <c r="H535" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I535" s="4" t="s">
         <v>16</v>
@@ -27566,13 +27570,13 @@
         <v>2015</v>
       </c>
       <c r="F536" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G536" s="1">
         <v>2015</v>
       </c>
       <c r="H536" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I536" s="4" t="s">
         <v>16</v>
@@ -27610,13 +27614,13 @@
         <v>2015</v>
       </c>
       <c r="F537" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G537" s="1">
         <v>2015</v>
       </c>
       <c r="H537" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="I537" s="4" t="s">
         <v>16</v>
@@ -27654,13 +27658,13 @@
         <v>2015</v>
       </c>
       <c r="F538" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G538" s="1">
         <v>2015</v>
       </c>
       <c r="H538" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="I538" s="4" t="s">
         <v>16</v>
@@ -27698,13 +27702,13 @@
         <v>2015</v>
       </c>
       <c r="F539" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G539" s="1">
         <v>2015</v>
       </c>
       <c r="H539" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I539" s="4" t="s">
         <v>16</v>
@@ -27742,13 +27746,13 @@
         <v>2015</v>
       </c>
       <c r="F540" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G540" s="1">
         <v>2015</v>
       </c>
       <c r="H540" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="I540" s="4" t="s">
         <v>16</v>
@@ -27786,13 +27790,13 @@
         <v>2015</v>
       </c>
       <c r="F541" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G541" s="1">
         <v>2015</v>
       </c>
       <c r="H541" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I541" s="4" t="s">
         <v>16</v>
@@ -27830,13 +27834,13 @@
         <v>2015</v>
       </c>
       <c r="F542" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G542" s="1">
         <v>2015</v>
       </c>
       <c r="H542" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="I542" s="4" t="s">
         <v>16</v>
@@ -27874,13 +27878,13 @@
         <v>2015</v>
       </c>
       <c r="F543" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G543" s="1">
         <v>2015</v>
       </c>
       <c r="H543" s="4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="I543" s="4" t="s">
         <v>16</v>
@@ -27918,13 +27922,13 @@
         <v>2015</v>
       </c>
       <c r="F544" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G544" s="1">
         <v>2015</v>
       </c>
       <c r="H544" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I544" s="4" t="s">
         <v>16</v>
@@ -27962,13 +27966,13 @@
         <v>2015</v>
       </c>
       <c r="F545" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="G545" s="1">
         <v>2015</v>
       </c>
       <c r="H545" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I545" s="4" t="s">
         <v>16</v>
@@ -28006,13 +28010,13 @@
         <v>2015</v>
       </c>
       <c r="F546" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="G546" s="1">
         <v>2015</v>
       </c>
       <c r="H546" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I546" s="4" t="s">
         <v>16</v>
@@ -28050,13 +28054,13 @@
         <v>2015</v>
       </c>
       <c r="F547" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G547" s="1">
         <v>2015</v>
       </c>
       <c r="H547" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I547" s="4" t="s">
         <v>16</v>
@@ -28094,13 +28098,13 @@
         <v>2015</v>
       </c>
       <c r="F548" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G548" s="1">
         <v>2015</v>
       </c>
       <c r="H548" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="I548" s="4" t="s">
         <v>16</v>
@@ -28138,13 +28142,13 @@
         <v>2015</v>
       </c>
       <c r="F549" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G549" s="1">
         <v>2015</v>
       </c>
       <c r="H549" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I549" s="4" t="s">
         <v>16</v>
@@ -28182,13 +28186,13 @@
         <v>2015</v>
       </c>
       <c r="F550" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G550" s="1">
         <v>2015</v>
       </c>
       <c r="H550" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="I550" s="4" t="s">
         <v>16</v>
@@ -28226,13 +28230,13 @@
         <v>2015</v>
       </c>
       <c r="F551" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G551" s="1">
         <v>2015</v>
       </c>
       <c r="H551" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I551" s="4" t="s">
         <v>16</v>
@@ -28270,13 +28274,13 @@
         <v>2015</v>
       </c>
       <c r="F552" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G552" s="1">
         <v>2015</v>
       </c>
       <c r="H552" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="I552" s="4" t="s">
         <v>16</v>
@@ -28314,13 +28318,13 @@
         <v>2015</v>
       </c>
       <c r="F553" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G553" s="1">
         <v>2015</v>
       </c>
       <c r="H553" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I553" s="4" t="s">
         <v>16</v>
@@ -28358,13 +28362,13 @@
         <v>2015</v>
       </c>
       <c r="F554" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G554" s="1">
         <v>2015</v>
       </c>
       <c r="H554" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I554" s="4" t="s">
         <v>16</v>
@@ -28402,13 +28406,13 @@
         <v>2015</v>
       </c>
       <c r="F555" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G555" s="1">
         <v>2015</v>
       </c>
       <c r="H555" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I555" s="4" t="s">
         <v>16</v>
@@ -28446,13 +28450,13 @@
         <v>2015</v>
       </c>
       <c r="F556" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G556" s="1">
         <v>2015</v>
       </c>
       <c r="H556" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I556" s="4" t="s">
         <v>16</v>
@@ -28490,13 +28494,13 @@
         <v>2015</v>
       </c>
       <c r="F557" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G557" s="1">
         <v>2015</v>
       </c>
       <c r="H557" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I557" s="4" t="s">
         <v>16</v>
@@ -28534,13 +28538,13 @@
         <v>2015</v>
       </c>
       <c r="F558" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G558" s="1">
         <v>2015</v>
       </c>
       <c r="H558" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I558" s="4" t="s">
         <v>16</v>
@@ -28578,13 +28582,13 @@
         <v>2015</v>
       </c>
       <c r="F559" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G559" s="1">
         <v>2015</v>
       </c>
       <c r="H559" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="I559" s="4" t="s">
         <v>16</v>
@@ -28622,13 +28626,13 @@
         <v>2015</v>
       </c>
       <c r="F560" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G560" s="1">
         <v>2015</v>
       </c>
       <c r="H560" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I560" s="4" t="s">
         <v>16</v>
@@ -28666,13 +28670,13 @@
         <v>2015</v>
       </c>
       <c r="F561" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G561" s="1">
         <v>2015</v>
       </c>
       <c r="H561" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="I561" s="4" t="s">
         <v>16</v>
@@ -28710,13 +28714,13 @@
         <v>2015</v>
       </c>
       <c r="F562" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G562" s="1">
         <v>2015</v>
       </c>
       <c r="H562" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="I562" s="4" t="s">
         <v>16</v>
@@ -28754,13 +28758,13 @@
         <v>2015</v>
       </c>
       <c r="F563" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G563" s="1">
         <v>2015</v>
       </c>
       <c r="H563" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="I563" s="4" t="s">
         <v>16</v>
@@ -28798,13 +28802,13 @@
         <v>2015</v>
       </c>
       <c r="F564" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G564" s="1">
         <v>2015</v>
       </c>
       <c r="H564" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="I564" s="4" t="s">
         <v>16</v>
@@ -28842,13 +28846,13 @@
         <v>2015</v>
       </c>
       <c r="F565" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G565" s="1">
         <v>2015</v>
       </c>
       <c r="H565" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="I565" s="4" t="s">
         <v>16</v>
@@ -28886,13 +28890,13 @@
         <v>2015</v>
       </c>
       <c r="F566" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G566" s="1">
         <v>2015</v>
       </c>
       <c r="H566" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="I566" s="4" t="s">
         <v>16</v>
@@ -28930,13 +28934,13 @@
         <v>2015</v>
       </c>
       <c r="F567" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G567" s="1">
         <v>2015</v>
       </c>
       <c r="H567" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I567" s="4" t="s">
         <v>16</v>
@@ -28974,13 +28978,13 @@
         <v>2015</v>
       </c>
       <c r="F568" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G568" s="1">
         <v>2015</v>
       </c>
       <c r="H568" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I568" s="4" t="s">
         <v>16</v>
@@ -29018,13 +29022,13 @@
         <v>2015</v>
       </c>
       <c r="F569" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G569" s="1">
         <v>2015</v>
       </c>
       <c r="H569" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="I569" s="4" t="s">
         <v>16</v>
@@ -29062,13 +29066,13 @@
         <v>2015</v>
       </c>
       <c r="F570" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G570" s="1">
         <v>2015</v>
       </c>
       <c r="H570" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="I570" s="4" t="s">
         <v>16</v>
@@ -29106,13 +29110,13 @@
         <v>2015</v>
       </c>
       <c r="F571" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G571" s="1">
         <v>2015</v>
       </c>
       <c r="H571" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="I571" s="4" t="s">
         <v>16</v>
@@ -29150,13 +29154,13 @@
         <v>2015</v>
       </c>
       <c r="F572" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G572" s="1">
         <v>2015</v>
       </c>
       <c r="H572" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="I572" s="4" t="s">
         <v>16</v>
@@ -29194,13 +29198,13 @@
         <v>2015</v>
       </c>
       <c r="F573" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G573" s="1">
         <v>2015</v>
       </c>
       <c r="H573" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I573" s="4" t="s">
         <v>16</v>
@@ -29238,13 +29242,13 @@
         <v>2015</v>
       </c>
       <c r="F574" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G574" s="1">
         <v>2015</v>
       </c>
       <c r="H574" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I574" s="4" t="s">
         <v>16</v>
@@ -29282,13 +29286,13 @@
         <v>2015</v>
       </c>
       <c r="F575" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G575" s="1">
         <v>2015</v>
       </c>
       <c r="H575" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I575" s="4" t="s">
         <v>16</v>
@@ -29326,13 +29330,13 @@
         <v>2015</v>
       </c>
       <c r="F576" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G576" s="1">
         <v>2015</v>
       </c>
       <c r="H576" s="4" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I576" s="4" t="s">
         <v>16</v>
@@ -29370,13 +29374,13 @@
         <v>2015</v>
       </c>
       <c r="F577" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G577" s="1">
         <v>2015</v>
       </c>
       <c r="H577" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="I577" s="4" t="s">
         <v>16</v>
@@ -29414,13 +29418,13 @@
         <v>2015</v>
       </c>
       <c r="F578" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G578" s="1">
         <v>2015</v>
       </c>
       <c r="H578" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="I578" s="4" t="s">
         <v>16</v>
@@ -29458,13 +29462,13 @@
         <v>2015</v>
       </c>
       <c r="F579" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G579" s="1">
         <v>2015</v>
       </c>
       <c r="H579" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I579" s="4" t="s">
         <v>16</v>
@@ -29502,13 +29506,13 @@
         <v>2015</v>
       </c>
       <c r="F580" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G580" s="1">
         <v>2015</v>
       </c>
       <c r="H580" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I580" s="4" t="s">
         <v>16</v>
@@ -29546,13 +29550,13 @@
         <v>2015</v>
       </c>
       <c r="F581" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G581" s="1">
         <v>2015</v>
       </c>
       <c r="H581" s="4" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="I581" s="4" t="s">
         <v>16</v>
@@ -29590,13 +29594,13 @@
         <v>2015</v>
       </c>
       <c r="F582" s="4" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G582" s="1">
         <v>2015</v>
       </c>
       <c r="H582" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I582" s="4" t="s">
         <v>16</v>
@@ -29634,13 +29638,13 @@
         <v>2015</v>
       </c>
       <c r="F583" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G583" s="1">
         <v>2015</v>
       </c>
       <c r="H583" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I583" s="4" t="s">
         <v>16</v>
@@ -29678,13 +29682,13 @@
         <v>2015</v>
       </c>
       <c r="F584" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="G584" s="1">
         <v>2015</v>
       </c>
       <c r="H584" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I584" s="4" t="s">
         <v>16</v>
@@ -29722,13 +29726,13 @@
         <v>2015</v>
       </c>
       <c r="F585" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G585" s="1">
         <v>2015</v>
       </c>
       <c r="H585" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="I585" s="4" t="s">
         <v>16</v>
@@ -29766,13 +29770,13 @@
         <v>2015</v>
       </c>
       <c r="F586" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G586" s="1">
         <v>2015</v>
       </c>
       <c r="H586" s="4" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I586" s="4" t="s">
         <v>16</v>
@@ -29810,13 +29814,13 @@
         <v>2015</v>
       </c>
       <c r="F587" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G587" s="1">
         <v>2015</v>
       </c>
       <c r="H587" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="I587" s="4" t="s">
         <v>16</v>
@@ -29854,13 +29858,13 @@
         <v>2015</v>
       </c>
       <c r="F588" s="4" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G588" s="1">
         <v>2015</v>
       </c>
       <c r="H588" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I588" s="4" t="s">
         <v>16</v>
@@ -29898,13 +29902,13 @@
         <v>2015</v>
       </c>
       <c r="F589" s="4" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="G589" s="1">
         <v>2015</v>
       </c>
       <c r="H589" s="4" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="I589" s="4" t="s">
         <v>16</v>
@@ -29942,13 +29946,13 @@
         <v>2015</v>
       </c>
       <c r="F590" s="4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G590" s="1">
         <v>2015</v>
       </c>
       <c r="H590" s="4" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="I590" s="4" t="s">
         <v>16</v>
@@ -29986,13 +29990,13 @@
         <v>2015</v>
       </c>
       <c r="F591" s="4" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G591" s="1">
         <v>2015</v>
       </c>
       <c r="H591" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I591" s="4" t="s">
         <v>16</v>
@@ -30030,13 +30034,13 @@
         <v>2015</v>
       </c>
       <c r="F592" s="4" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G592" s="1">
         <v>2015</v>
       </c>
       <c r="H592" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="I592" s="4" t="s">
         <v>16</v>
@@ -30074,13 +30078,13 @@
         <v>2015</v>
       </c>
       <c r="F593" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G593" s="1">
         <v>2015</v>
       </c>
       <c r="H593" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="I593" s="4" t="s">
         <v>16</v>
@@ -30118,13 +30122,13 @@
         <v>2015</v>
       </c>
       <c r="F594" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G594" s="1">
         <v>2015</v>
       </c>
       <c r="H594" s="4" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="I594" s="4" t="s">
         <v>16</v>
@@ -30162,13 +30166,13 @@
         <v>2015</v>
       </c>
       <c r="F595" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G595" s="1">
         <v>2015</v>
       </c>
       <c r="H595" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="I595" s="4" t="s">
         <v>16</v>
@@ -30206,13 +30210,13 @@
         <v>2015</v>
       </c>
       <c r="F596" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G596" s="1">
         <v>2015</v>
       </c>
       <c r="H596" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I596" s="4" t="s">
         <v>16</v>
@@ -30250,13 +30254,13 @@
         <v>2015</v>
       </c>
       <c r="F597" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G597" s="1">
         <v>2015</v>
       </c>
       <c r="H597" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="I597" s="4" t="s">
         <v>16</v>
@@ -30294,13 +30298,13 @@
         <v>2015</v>
       </c>
       <c r="F598" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G598" s="1">
         <v>2015</v>
       </c>
       <c r="H598" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="I598" s="4" t="s">
         <v>16</v>
@@ -30338,13 +30342,13 @@
         <v>2015</v>
       </c>
       <c r="F599" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G599" s="1">
         <v>2015</v>
       </c>
       <c r="H599" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I599" s="4" t="s">
         <v>16</v>
@@ -30382,13 +30386,13 @@
         <v>2015</v>
       </c>
       <c r="F600" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G600" s="1">
         <v>2015</v>
       </c>
       <c r="H600" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="I600" s="4" t="s">
         <v>16</v>
@@ -30426,13 +30430,13 @@
         <v>2015</v>
       </c>
       <c r="F601" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G601" s="1">
         <v>2015</v>
       </c>
       <c r="H601" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="I601" s="4" t="s">
         <v>16</v>
@@ -30470,13 +30474,13 @@
         <v>2015</v>
       </c>
       <c r="F602" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G602" s="1">
         <v>2015</v>
       </c>
       <c r="H602" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="I602" s="4" t="s">
         <v>16</v>
@@ -30514,13 +30518,13 @@
         <v>2015</v>
       </c>
       <c r="F603" s="4" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G603" s="1">
         <v>2015</v>
       </c>
       <c r="H603" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="I603" s="4" t="s">
         <v>16</v>
@@ -30558,13 +30562,13 @@
         <v>2015</v>
       </c>
       <c r="F604" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G604" s="1">
         <v>2015</v>
       </c>
       <c r="H604" s="4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="I604" s="4" t="s">
         <v>16</v>
@@ -30602,13 +30606,13 @@
         <v>2015</v>
       </c>
       <c r="F605" s="4" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G605" s="1">
         <v>2015</v>
       </c>
       <c r="H605" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="I605" s="4" t="s">
         <v>16</v>
@@ -30646,13 +30650,13 @@
         <v>2015</v>
       </c>
       <c r="F606" s="4" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G606" s="1">
         <v>2015</v>
       </c>
       <c r="H606" s="4" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="I606" s="4" t="s">
         <v>16</v>
@@ -30690,13 +30694,13 @@
         <v>2015</v>
       </c>
       <c r="F607" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G607" s="1">
         <v>2015</v>
       </c>
       <c r="H607" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="I607" s="4" t="s">
         <v>16</v>
@@ -30734,13 +30738,13 @@
         <v>2015</v>
       </c>
       <c r="F608" s="4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G608" s="1">
         <v>2015</v>
       </c>
       <c r="H608" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="I608" s="4" t="s">
         <v>16</v>
@@ -30778,13 +30782,13 @@
         <v>2015</v>
       </c>
       <c r="F609" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G609" s="1">
         <v>2015</v>
       </c>
       <c r="H609" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="I609" s="4" t="s">
         <v>16</v>
@@ -30822,13 +30826,13 @@
         <v>2015</v>
       </c>
       <c r="F610" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="G610" s="1">
         <v>2015</v>
       </c>
       <c r="H610" s="4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="I610" s="4" t="s">
         <v>16</v>
@@ -30866,13 +30870,13 @@
         <v>2015</v>
       </c>
       <c r="F611" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G611" s="1">
         <v>2015</v>
       </c>
       <c r="H611" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="I611" s="4" t="s">
         <v>16</v>
@@ -30910,13 +30914,13 @@
         <v>2015</v>
       </c>
       <c r="F612" s="4" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G612" s="1">
         <v>2015</v>
       </c>
       <c r="H612" s="4" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I612" s="4" t="s">
         <v>16</v>
@@ -30954,13 +30958,13 @@
         <v>2015</v>
       </c>
       <c r="F613" s="4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="G613" s="1">
         <v>2015</v>
       </c>
       <c r="H613" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="I613" s="4" t="s">
         <v>16</v>
@@ -30998,13 +31002,13 @@
         <v>2015</v>
       </c>
       <c r="F614" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G614" s="1">
         <v>2015</v>
       </c>
       <c r="H614" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="I614" s="4" t="s">
         <v>16</v>
@@ -31042,13 +31046,13 @@
         <v>2015</v>
       </c>
       <c r="F615" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="G615" s="1">
         <v>2015</v>
       </c>
       <c r="H615" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="I615" s="4" t="s">
         <v>16</v>
@@ -31086,13 +31090,13 @@
         <v>2015</v>
       </c>
       <c r="F616" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G616" s="1">
         <v>2015</v>
       </c>
       <c r="H616" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="I616" s="4" t="s">
         <v>16</v>
@@ -31130,13 +31134,13 @@
         <v>2015</v>
       </c>
       <c r="F617" s="4" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="G617" s="1">
         <v>2015</v>
       </c>
       <c r="H617" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="I617" s="4" t="s">
         <v>16</v>
@@ -31174,13 +31178,13 @@
         <v>2015</v>
       </c>
       <c r="F618" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G618" s="1">
         <v>2015</v>
       </c>
       <c r="H618" s="4" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="I618" s="4" t="s">
         <v>16</v>
@@ -31218,13 +31222,13 @@
         <v>2015</v>
       </c>
       <c r="F619" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="G619" s="1">
         <v>2015</v>
       </c>
       <c r="H619" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="I619" s="4" t="s">
         <v>16</v>
@@ -31262,13 +31266,13 @@
         <v>2015</v>
       </c>
       <c r="F620" s="4" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G620" s="1">
         <v>2015</v>
       </c>
       <c r="H620" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="I620" s="4" t="s">
         <v>16</v>
@@ -31306,13 +31310,13 @@
         <v>2015</v>
       </c>
       <c r="F621" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G621" s="1">
         <v>2015</v>
       </c>
       <c r="H621" s="4" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="I621" s="4" t="s">
         <v>16</v>
@@ -31350,13 +31354,13 @@
         <v>2015</v>
       </c>
       <c r="F622" s="4" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G622" s="1">
         <v>2015</v>
       </c>
       <c r="H622" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I622" s="4" t="s">
         <v>16</v>
@@ -31394,13 +31398,13 @@
         <v>2015</v>
       </c>
       <c r="F623" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G623" s="1">
         <v>2015</v>
       </c>
       <c r="H623" s="4" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="I623" s="4" t="s">
         <v>16</v>
@@ -31438,13 +31442,13 @@
         <v>2015</v>
       </c>
       <c r="F624" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G624" s="1">
         <v>2015</v>
       </c>
       <c r="H624" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="I624" s="4" t="s">
         <v>16</v>
@@ -31482,13 +31486,13 @@
         <v>2015</v>
       </c>
       <c r="F625" s="4" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="G625" s="1">
         <v>2015</v>
       </c>
       <c r="H625" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="I625" s="4" t="s">
         <v>16</v>
@@ -31526,13 +31530,13 @@
         <v>2015</v>
       </c>
       <c r="F626" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="G626" s="1">
         <v>2015</v>
       </c>
       <c r="H626" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I626" s="4" t="s">
         <v>16</v>
@@ -31570,13 +31574,13 @@
         <v>2015</v>
       </c>
       <c r="F627" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="G627" s="1">
         <v>2015</v>
       </c>
       <c r="H627" s="4" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I627" s="4" t="s">
         <v>16</v>
@@ -31614,13 +31618,13 @@
         <v>2015</v>
       </c>
       <c r="F628" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="G628" s="1">
         <v>2015</v>
       </c>
       <c r="H628" s="4" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="I628" s="4" t="s">
         <v>16</v>
@@ -31658,13 +31662,13 @@
         <v>2015</v>
       </c>
       <c r="F629" s="4" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="G629" s="1">
         <v>2015</v>
       </c>
       <c r="H629" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="I629" s="4" t="s">
         <v>16</v>
@@ -31702,13 +31706,13 @@
         <v>2015</v>
       </c>
       <c r="F630" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G630" s="1">
         <v>2015</v>
       </c>
       <c r="H630" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="I630" s="4" t="s">
         <v>16</v>
@@ -31746,13 +31750,13 @@
         <v>2015</v>
       </c>
       <c r="F631" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G631" s="1">
         <v>2015</v>
       </c>
       <c r="H631" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="I631" s="4" t="s">
         <v>16</v>
@@ -31790,13 +31794,13 @@
         <v>2015</v>
       </c>
       <c r="F632" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G632" s="1">
         <v>2015</v>
       </c>
       <c r="H632" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="I632" s="4" t="s">
         <v>16</v>
@@ -31834,13 +31838,13 @@
         <v>2015</v>
       </c>
       <c r="F633" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G633" s="1">
         <v>2015</v>
       </c>
       <c r="H633" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I633" s="4" t="s">
         <v>16</v>
@@ -31878,13 +31882,13 @@
         <v>2015</v>
       </c>
       <c r="F634" s="4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G634" s="1">
         <v>2015</v>
       </c>
       <c r="H634" s="4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I634" s="4" t="s">
         <v>16</v>
@@ -31922,13 +31926,13 @@
         <v>2015</v>
       </c>
       <c r="F635" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G635" s="1">
         <v>2015</v>
       </c>
       <c r="H635" s="4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="I635" s="4" t="s">
         <v>16</v>
@@ -31966,13 +31970,13 @@
         <v>2015</v>
       </c>
       <c r="F636" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="G636" s="1">
         <v>2015</v>
       </c>
       <c r="H636" s="4" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="I636" s="4" t="s">
         <v>16</v>
@@ -32010,13 +32014,13 @@
         <v>2015</v>
       </c>
       <c r="F637" s="4" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="G637" s="1">
         <v>2015</v>
       </c>
       <c r="H637" s="4" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I637" s="4" t="s">
         <v>16</v>
@@ -32054,13 +32058,13 @@
         <v>2015</v>
       </c>
       <c r="F638" s="4" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="G638" s="1">
         <v>2015</v>
       </c>
       <c r="H638" s="4" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="I638" s="4" t="s">
         <v>16</v>
@@ -32098,13 +32102,13 @@
         <v>2015</v>
       </c>
       <c r="F639" s="4" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G639" s="1">
         <v>2015</v>
       </c>
       <c r="H639" s="4" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="I639" s="4" t="s">
         <v>16</v>
@@ -32142,13 +32146,13 @@
         <v>2015</v>
       </c>
       <c r="F640" s="4" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G640" s="1">
         <v>2015</v>
       </c>
       <c r="H640" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="I640" s="4" t="s">
         <v>16</v>
@@ -32186,13 +32190,13 @@
         <v>2015</v>
       </c>
       <c r="F641" s="4" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="G641" s="1">
         <v>2015</v>
       </c>
       <c r="H641" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="I641" s="4" t="s">
         <v>16</v>
@@ -32230,13 +32234,13 @@
         <v>2015</v>
       </c>
       <c r="F642" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G642" s="1">
         <v>2015</v>
       </c>
       <c r="H642" s="4" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="I642" s="4" t="s">
         <v>16</v>
@@ -32274,13 +32278,13 @@
         <v>2015</v>
       </c>
       <c r="F643" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="G643" s="1">
         <v>2015</v>
       </c>
       <c r="H643" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="I643" s="4" t="s">
         <v>16</v>
@@ -32318,13 +32322,13 @@
         <v>2015</v>
       </c>
       <c r="F644" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="G644" s="1">
         <v>2015</v>
       </c>
       <c r="H644" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="I644" s="4" t="s">
         <v>16</v>
@@ -32362,13 +32366,13 @@
         <v>2015</v>
       </c>
       <c r="F645" s="4" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G645" s="1">
         <v>2015</v>
       </c>
       <c r="H645" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="I645" s="4" t="s">
         <v>16</v>
@@ -32406,13 +32410,13 @@
         <v>2015</v>
       </c>
       <c r="F646" s="4" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G646" s="1">
         <v>2015</v>
       </c>
       <c r="H646" s="4" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="I646" s="4" t="s">
         <v>16</v>
@@ -32450,13 +32454,13 @@
         <v>2015</v>
       </c>
       <c r="F647" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G647" s="1">
         <v>2015</v>
       </c>
       <c r="H647" s="4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="I647" s="4" t="s">
         <v>16</v>
@@ -32494,13 +32498,13 @@
         <v>2015</v>
       </c>
       <c r="F648" s="4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="G648" s="1">
         <v>2015</v>
       </c>
       <c r="H648" s="4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="I648" s="4" t="s">
         <v>16</v>
@@ -32538,13 +32542,13 @@
         <v>2015</v>
       </c>
       <c r="F649" s="4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G649" s="1">
         <v>2015</v>
       </c>
       <c r="H649" s="4" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="I649" s="4" t="s">
         <v>16</v>
@@ -32582,13 +32586,13 @@
         <v>2015</v>
       </c>
       <c r="F650" s="4" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G650" s="1">
         <v>2015</v>
       </c>
       <c r="H650" s="4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="I650" s="4" t="s">
         <v>16</v>
@@ -32626,13 +32630,13 @@
         <v>2015</v>
       </c>
       <c r="F651" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="G651" s="1">
         <v>2015</v>
       </c>
       <c r="H651" s="4" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="I651" s="4" t="s">
         <v>16</v>
@@ -32670,13 +32674,13 @@
         <v>2015</v>
       </c>
       <c r="F652" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="G652" s="1">
         <v>2015</v>
       </c>
       <c r="H652" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I652" s="4" t="s">
         <v>16</v>
@@ -32714,13 +32718,13 @@
         <v>2015</v>
       </c>
       <c r="F653" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G653" s="1">
         <v>2015</v>
       </c>
       <c r="H653" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="I653" s="4" t="s">
         <v>16</v>
@@ -32758,13 +32762,13 @@
         <v>2015</v>
       </c>
       <c r="F654" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G654" s="1">
         <v>2015</v>
       </c>
       <c r="H654" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="I654" s="4" t="s">
         <v>16</v>
@@ -32802,13 +32806,13 @@
         <v>2015</v>
       </c>
       <c r="F655" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="G655" s="1">
         <v>2015</v>
       </c>
       <c r="H655" s="4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="I655" s="4" t="s">
         <v>16</v>
@@ -32846,13 +32850,13 @@
         <v>2015</v>
       </c>
       <c r="F656" s="4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G656" s="1">
         <v>2015</v>
       </c>
       <c r="H656" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="I656" s="4" t="s">
         <v>16</v>
@@ -32890,13 +32894,13 @@
         <v>2015</v>
       </c>
       <c r="F657" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G657" s="1">
         <v>2015</v>
       </c>
       <c r="H657" s="4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="I657" s="4" t="s">
         <v>16</v>
@@ -32934,13 +32938,13 @@
         <v>2015</v>
       </c>
       <c r="F658" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G658" s="1">
         <v>2015</v>
       </c>
       <c r="H658" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="I658" s="4" t="s">
         <v>16</v>
@@ -32978,13 +32982,13 @@
         <v>2015</v>
       </c>
       <c r="F659" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G659" s="1">
         <v>2015</v>
       </c>
       <c r="H659" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="I659" s="4" t="s">
         <v>16</v>
@@ -33022,13 +33026,13 @@
         <v>2015</v>
       </c>
       <c r="F660" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="G660" s="1">
         <v>2015</v>
       </c>
       <c r="H660" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="I660" s="4" t="s">
         <v>16</v>
@@ -33066,13 +33070,13 @@
         <v>2015</v>
       </c>
       <c r="F661" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G661" s="1">
         <v>2015</v>
       </c>
       <c r="H661" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="I661" s="4" t="s">
         <v>16</v>
@@ -33110,13 +33114,13 @@
         <v>2015</v>
       </c>
       <c r="F662" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G662" s="1">
         <v>2015</v>
       </c>
       <c r="H662" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="I662" s="4" t="s">
         <v>16</v>
@@ -33154,13 +33158,13 @@
         <v>2015</v>
       </c>
       <c r="F663" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G663" s="1">
         <v>2015</v>
       </c>
       <c r="H663" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="I663" s="4" t="s">
         <v>16</v>
@@ -33198,13 +33202,13 @@
         <v>2015</v>
       </c>
       <c r="F664" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G664" s="1">
         <v>2015</v>
       </c>
       <c r="H664" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="I664" s="4" t="s">
         <v>16</v>
@@ -33242,13 +33246,13 @@
         <v>2015</v>
       </c>
       <c r="F665" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="G665" s="1">
         <v>2015</v>
       </c>
       <c r="H665" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="I665" s="4" t="s">
         <v>16</v>
@@ -33286,13 +33290,13 @@
         <v>2015</v>
       </c>
       <c r="F666" s="4" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G666" s="1">
         <v>2015</v>
       </c>
       <c r="H666" s="4" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="I666" s="4" t="s">
         <v>16</v>
@@ -33330,13 +33334,13 @@
         <v>2015</v>
       </c>
       <c r="F667" s="4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="G667" s="1">
         <v>2015</v>
       </c>
       <c r="H667" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="I667" s="4" t="s">
         <v>16</v>
@@ -33374,13 +33378,13 @@
         <v>2015</v>
       </c>
       <c r="F668" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="G668" s="1">
         <v>2015</v>
       </c>
       <c r="H668" s="4" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="I668" s="4" t="s">
         <v>16</v>
@@ -33418,13 +33422,13 @@
         <v>2015</v>
       </c>
       <c r="F669" s="4" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="G669" s="1">
         <v>2015</v>
       </c>
       <c r="H669" s="4" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="I669" s="4" t="s">
         <v>16</v>
@@ -33462,13 +33466,13 @@
         <v>2015</v>
       </c>
       <c r="F670" s="4" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G670" s="1">
         <v>2015</v>
       </c>
       <c r="H670" s="4" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I670" s="4" t="s">
         <v>16</v>
@@ -33506,13 +33510,13 @@
         <v>2015</v>
       </c>
       <c r="F671" s="4" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G671" s="1">
         <v>2015</v>
       </c>
       <c r="H671" s="4" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="I671" s="4" t="s">
         <v>16</v>
@@ -33550,13 +33554,13 @@
         <v>2015</v>
       </c>
       <c r="F672" s="4" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="G672" s="1">
         <v>2015</v>
       </c>
       <c r="H672" s="4" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="I672" s="4" t="s">
         <v>16</v>
@@ -33594,13 +33598,13 @@
         <v>2015</v>
       </c>
       <c r="F673" s="4" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G673" s="1">
         <v>2015</v>
       </c>
       <c r="H673" s="4" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="I673" s="4" t="s">
         <v>16</v>
@@ -33638,13 +33642,13 @@
         <v>2015</v>
       </c>
       <c r="F674" s="4" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G674" s="1">
         <v>2015</v>
       </c>
       <c r="H674" s="4" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="I674" s="4" t="s">
         <v>16</v>
@@ -33682,13 +33686,13 @@
         <v>2015</v>
       </c>
       <c r="F675" s="4" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="G675" s="1">
         <v>2015</v>
       </c>
       <c r="H675" s="4" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="I675" s="4" t="s">
         <v>16</v>
@@ -33726,13 +33730,13 @@
         <v>2015</v>
       </c>
       <c r="F676" s="4" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G676" s="1">
         <v>2015</v>
       </c>
       <c r="H676" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="I676" s="4" t="s">
         <v>16</v>
@@ -33770,13 +33774,13 @@
         <v>2015</v>
       </c>
       <c r="F677" s="4" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G677" s="1">
         <v>2015</v>
       </c>
       <c r="H677" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I677" s="4" t="s">
         <v>16</v>
@@ -33814,13 +33818,13 @@
         <v>2015</v>
       </c>
       <c r="F678" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G678" s="1">
         <v>2015</v>
       </c>
       <c r="H678" s="4" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="I678" s="4" t="s">
         <v>16</v>
@@ -33858,13 +33862,13 @@
         <v>2015</v>
       </c>
       <c r="F679" s="4" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G679" s="1">
         <v>2015</v>
       </c>
       <c r="H679" s="4" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="I679" s="4" t="s">
         <v>16</v>
@@ -33902,13 +33906,13 @@
         <v>2015</v>
       </c>
       <c r="F680" s="4" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="G680" s="1">
         <v>2015</v>
       </c>
       <c r="H680" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I680" s="4" t="s">
         <v>16</v>
@@ -33946,13 +33950,13 @@
         <v>2015</v>
       </c>
       <c r="F681" s="4" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="G681" s="1">
         <v>2015</v>
       </c>
       <c r="H681" s="4" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="I681" s="4" t="s">
         <v>16</v>
@@ -33990,13 +33994,13 @@
         <v>2015</v>
       </c>
       <c r="F682" s="4" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G682" s="1">
         <v>2015</v>
       </c>
       <c r="H682" s="4" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="I682" s="4" t="s">
         <v>16</v>
@@ -34034,13 +34038,13 @@
         <v>2015</v>
       </c>
       <c r="F683" s="4" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G683" s="1">
         <v>2015</v>
       </c>
       <c r="H683" s="4" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="I683" s="4" t="s">
         <v>16</v>
@@ -34078,13 +34082,13 @@
         <v>2015</v>
       </c>
       <c r="F684" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G684" s="1">
         <v>2015</v>
       </c>
       <c r="H684" s="4" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="I684" s="4" t="s">
         <v>16</v>
@@ -34122,13 +34126,13 @@
         <v>2015</v>
       </c>
       <c r="F685" s="4" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G685" s="1">
         <v>2015</v>
       </c>
       <c r="H685" s="4" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I685" s="4" t="s">
         <v>16</v>
@@ -34166,13 +34170,13 @@
         <v>2015</v>
       </c>
       <c r="F686" s="4" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="G686" s="1">
         <v>2015</v>
       </c>
       <c r="H686" s="4" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="I686" s="4" t="s">
         <v>16</v>
@@ -34210,13 +34214,13 @@
         <v>2015</v>
       </c>
       <c r="F687" s="4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="G687" s="1">
         <v>2015</v>
       </c>
       <c r="H687" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="I687" s="4" t="s">
         <v>16</v>
@@ -34254,13 +34258,13 @@
         <v>2015</v>
       </c>
       <c r="F688" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G688" s="1">
         <v>2015</v>
       </c>
       <c r="H688" s="4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="I688" s="4" t="s">
         <v>16</v>
@@ -34298,13 +34302,13 @@
         <v>2015</v>
       </c>
       <c r="F689" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G689" s="1">
         <v>2015</v>
       </c>
       <c r="H689" s="4" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="I689" s="4" t="s">
         <v>16</v>
@@ -34342,13 +34346,13 @@
         <v>2015</v>
       </c>
       <c r="F690" s="4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="G690" s="1">
         <v>2015</v>
       </c>
       <c r="H690" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="I690" s="4" t="s">
         <v>16</v>
@@ -34386,13 +34390,13 @@
         <v>2015</v>
       </c>
       <c r="F691" s="4" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G691" s="1">
         <v>2015</v>
       </c>
       <c r="H691" s="4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="I691" s="4" t="s">
         <v>16</v>
@@ -34430,13 +34434,13 @@
         <v>2015</v>
       </c>
       <c r="F692" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G692" s="1">
         <v>2015</v>
       </c>
       <c r="H692" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="I692" s="4" t="s">
         <v>16</v>
@@ -34474,13 +34478,13 @@
         <v>2015</v>
       </c>
       <c r="F693" s="4" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="G693" s="1">
         <v>2015</v>
       </c>
       <c r="H693" s="4" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="I693" s="4" t="s">
         <v>16</v>
@@ -34518,13 +34522,13 @@
         <v>2015</v>
       </c>
       <c r="F694" s="4" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="G694" s="1">
         <v>2015</v>
       </c>
       <c r="H694" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="I694" s="4" t="s">
         <v>16</v>
@@ -34562,13 +34566,13 @@
         <v>2015</v>
       </c>
       <c r="F695" s="4" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G695" s="1">
         <v>2015</v>
       </c>
       <c r="H695" s="4" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="I695" s="4" t="s">
         <v>16</v>
@@ -34606,13 +34610,13 @@
         <v>2015</v>
       </c>
       <c r="F696" s="4" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G696" s="1">
         <v>2015</v>
       </c>
       <c r="H696" s="4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="I696" s="4" t="s">
         <v>16</v>
@@ -34650,13 +34654,13 @@
         <v>2015</v>
       </c>
       <c r="F697" s="4" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G697" s="1">
         <v>2015</v>
       </c>
       <c r="H697" s="4" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="I697" s="4" t="s">
         <v>16</v>
@@ -34694,13 +34698,13 @@
         <v>2015</v>
       </c>
       <c r="F698" s="4" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G698" s="1">
         <v>2015</v>
       </c>
       <c r="H698" s="4" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="I698" s="4" t="s">
         <v>16</v>
@@ -34738,13 +34742,13 @@
         <v>2015</v>
       </c>
       <c r="F699" s="4" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="G699" s="1">
         <v>2015</v>
       </c>
       <c r="H699" s="4" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="I699" s="4" t="s">
         <v>16</v>
@@ -34782,13 +34786,13 @@
         <v>2015</v>
       </c>
       <c r="F700" s="4" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G700" s="1">
         <v>2015</v>
       </c>
       <c r="H700" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="I700" s="4" t="s">
         <v>16</v>
@@ -34826,13 +34830,13 @@
         <v>2015</v>
       </c>
       <c r="F701" s="4" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G701" s="1">
         <v>2015</v>
       </c>
       <c r="H701" s="4" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="I701" s="4" t="s">
         <v>16</v>
@@ -34870,13 +34874,13 @@
         <v>2015</v>
       </c>
       <c r="F702" s="4" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G702" s="1">
         <v>2015</v>
       </c>
       <c r="H702" s="4" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="I702" s="4" t="s">
         <v>16</v>
@@ -34914,13 +34918,13 @@
         <v>2015</v>
       </c>
       <c r="F703" s="4" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="G703" s="1">
         <v>2015</v>
       </c>
       <c r="H703" s="4" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="I703" s="4" t="s">
         <v>16</v>
@@ -34958,13 +34962,13 @@
         <v>2015</v>
       </c>
       <c r="F704" s="4" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G704" s="1">
         <v>2015</v>
       </c>
       <c r="H704" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="I704" s="4" t="s">
         <v>16</v>
@@ -35002,13 +35006,13 @@
         <v>2015</v>
       </c>
       <c r="F705" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G705" s="1">
         <v>2015</v>
       </c>
       <c r="H705" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="I705" s="4" t="s">
         <v>16</v>
@@ -35046,13 +35050,13 @@
         <v>2015</v>
       </c>
       <c r="F706" s="4" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="G706" s="1">
         <v>2015</v>
       </c>
       <c r="H706" s="4" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="I706" s="4" t="s">
         <v>16</v>
@@ -35090,13 +35094,13 @@
         <v>2015</v>
       </c>
       <c r="F707" s="4" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G707" s="1">
         <v>2015</v>
       </c>
       <c r="H707" s="4" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="I707" s="4" t="s">
         <v>16</v>
@@ -35134,13 +35138,13 @@
         <v>2015</v>
       </c>
       <c r="F708" s="4" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G708" s="1">
         <v>2015</v>
       </c>
       <c r="H708" s="4" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="I708" s="4" t="s">
         <v>16</v>
@@ -35178,13 +35182,13 @@
         <v>2015</v>
       </c>
       <c r="F709" s="4" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G709" s="1">
         <v>2015</v>
       </c>
       <c r="H709" s="4" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="I709" s="4" t="s">
         <v>16</v>
@@ -35222,13 +35226,13 @@
         <v>2015</v>
       </c>
       <c r="F710" s="4" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="G710" s="1">
         <v>2015</v>
       </c>
       <c r="H710" s="4" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="I710" s="4" t="s">
         <v>16</v>
@@ -35266,13 +35270,13 @@
         <v>2015</v>
       </c>
       <c r="F711" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="G711" s="1">
         <v>2015</v>
       </c>
       <c r="H711" s="4" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="I711" s="4" t="s">
         <v>16</v>
@@ -35310,13 +35314,13 @@
         <v>2015</v>
       </c>
       <c r="F712" s="4" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G712" s="1">
         <v>2015</v>
       </c>
       <c r="H712" s="4" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="I712" s="4" t="s">
         <v>16</v>
@@ -35354,13 +35358,13 @@
         <v>2015</v>
       </c>
       <c r="F713" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="G713" s="1">
         <v>2015</v>
       </c>
       <c r="H713" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="I713" s="4" t="s">
         <v>16</v>
@@ -35398,13 +35402,13 @@
         <v>2015</v>
       </c>
       <c r="F714" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G714" s="1">
         <v>2015</v>
       </c>
       <c r="H714" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="I714" s="4" t="s">
         <v>16</v>
@@ -35442,13 +35446,13 @@
         <v>2015</v>
       </c>
       <c r="F715" s="4" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="G715" s="1">
         <v>2015</v>
       </c>
       <c r="H715" s="4" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="I715" s="4" t="s">
         <v>16</v>
@@ -35486,13 +35490,13 @@
         <v>2015</v>
       </c>
       <c r="F716" s="4" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G716" s="1">
         <v>2015</v>
       </c>
       <c r="H716" s="4" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I716" s="4" t="s">
         <v>16</v>
@@ -35530,13 +35534,13 @@
         <v>2015</v>
       </c>
       <c r="F717" s="4" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="G717" s="1">
         <v>2015</v>
       </c>
       <c r="H717" s="4" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="I717" s="4" t="s">
         <v>16</v>
@@ -35574,13 +35578,13 @@
         <v>2015</v>
       </c>
       <c r="F718" s="4" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="G718" s="1">
         <v>2015</v>
       </c>
       <c r="H718" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="I718" s="4" t="s">
         <v>16</v>
@@ -35618,13 +35622,13 @@
         <v>2015</v>
       </c>
       <c r="F719" s="4" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="G719" s="1">
         <v>2015</v>
       </c>
       <c r="H719" s="4" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="I719" s="4" t="s">
         <v>16</v>
@@ -35662,13 +35666,13 @@
         <v>2015</v>
       </c>
       <c r="F720" s="4" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="G720" s="1">
         <v>2015</v>
       </c>
       <c r="H720" s="4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="I720" s="4" t="s">
         <v>16</v>
@@ -35706,13 +35710,13 @@
         <v>2015</v>
       </c>
       <c r="F721" s="4" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G721" s="1">
         <v>2015</v>
       </c>
       <c r="H721" s="4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="I721" s="4" t="s">
         <v>16</v>
@@ -35750,13 +35754,13 @@
         <v>2015</v>
       </c>
       <c r="F722" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G722" s="1">
         <v>2015</v>
       </c>
       <c r="H722" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="I722" s="4" t="s">
         <v>16</v>
@@ -35794,13 +35798,13 @@
         <v>2015</v>
       </c>
       <c r="F723" s="4" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G723" s="1">
         <v>2015</v>
       </c>
       <c r="H723" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="I723" s="4" t="s">
         <v>16</v>
@@ -35838,13 +35842,13 @@
         <v>2015</v>
       </c>
       <c r="F724" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="G724" s="1">
         <v>2015</v>
       </c>
       <c r="H724" s="4" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="I724" s="4" t="s">
         <v>16</v>
@@ -35882,13 +35886,13 @@
         <v>2015</v>
       </c>
       <c r="F725" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="G725" s="1">
         <v>2015</v>
       </c>
       <c r="H725" s="4" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="I725" s="4" t="s">
         <v>16</v>
@@ -35926,13 +35930,13 @@
         <v>2015</v>
       </c>
       <c r="F726" s="4" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G726" s="1">
         <v>2015</v>
       </c>
       <c r="H726" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="I726" s="4" t="s">
         <v>16</v>
@@ -35970,13 +35974,13 @@
         <v>2015</v>
       </c>
       <c r="F727" s="4" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G727" s="1">
         <v>2015</v>
       </c>
       <c r="H727" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="I727" s="4" t="s">
         <v>16</v>
@@ -36014,13 +36018,13 @@
         <v>2015</v>
       </c>
       <c r="F728" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G728" s="1">
         <v>2015</v>
       </c>
       <c r="H728" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="I728" s="4" t="s">
         <v>16</v>
@@ -36058,13 +36062,13 @@
         <v>2015</v>
       </c>
       <c r="F729" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G729" s="1">
         <v>2015</v>
       </c>
       <c r="H729" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="I729" s="4" t="s">
         <v>16</v>
@@ -36102,13 +36106,13 @@
         <v>2015</v>
       </c>
       <c r="F730" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G730" s="1">
         <v>2015</v>
       </c>
       <c r="H730" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="I730" s="4" t="s">
         <v>16</v>
@@ -36146,13 +36150,13 @@
         <v>2015</v>
       </c>
       <c r="F731" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="G731" s="1">
         <v>2015</v>
       </c>
       <c r="H731" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="I731" s="4" t="s">
         <v>16</v>
@@ -36190,13 +36194,13 @@
         <v>2015</v>
       </c>
       <c r="F732" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G732" s="1">
         <v>2015</v>
       </c>
       <c r="H732" s="4" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="I732" s="4" t="s">
         <v>16</v>
@@ -36234,13 +36238,13 @@
         <v>2015</v>
       </c>
       <c r="F733" s="4" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G733" s="1">
         <v>2015</v>
       </c>
       <c r="H733" s="4" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="I733" s="4" t="s">
         <v>16</v>
@@ -36278,13 +36282,13 @@
         <v>2015</v>
       </c>
       <c r="F734" s="4" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G734" s="1">
         <v>2015</v>
       </c>
       <c r="H734" s="4" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="I734" s="4" t="s">
         <v>16</v>
@@ -36322,13 +36326,13 @@
         <v>2015</v>
       </c>
       <c r="F735" s="4" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G735" s="1">
         <v>2015</v>
       </c>
       <c r="H735" s="4" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="I735" s="4" t="s">
         <v>16</v>
@@ -36366,13 +36370,13 @@
         <v>2015</v>
       </c>
       <c r="F736" s="4" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="G736" s="1">
         <v>2015</v>
       </c>
       <c r="H736" s="4" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="I736" s="4" t="s">
         <v>16</v>
@@ -36410,13 +36414,13 @@
         <v>2015</v>
       </c>
       <c r="F737" s="4" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G737" s="1">
         <v>2015</v>
       </c>
       <c r="H737" s="4" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="I737" s="4" t="s">
         <v>16</v>
@@ -36454,13 +36458,13 @@
         <v>2015</v>
       </c>
       <c r="F738" s="4" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G738" s="1">
         <v>2015</v>
       </c>
       <c r="H738" s="4" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="I738" s="4" t="s">
         <v>16</v>
@@ -36498,13 +36502,13 @@
         <v>2015</v>
       </c>
       <c r="F739" s="4" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="G739" s="1">
         <v>2015</v>
       </c>
       <c r="H739" s="4" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="I739" s="4" t="s">
         <v>16</v>
@@ -36542,13 +36546,13 @@
         <v>2015</v>
       </c>
       <c r="F740" s="4" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="G740" s="1">
         <v>2015</v>
       </c>
       <c r="H740" s="4" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="I740" s="4" t="s">
         <v>16</v>
@@ -36586,13 +36590,13 @@
         <v>2015</v>
       </c>
       <c r="F741" s="4" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="G741" s="1">
         <v>2015</v>
       </c>
       <c r="H741" s="4" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="I741" s="4" t="s">
         <v>16</v>
@@ -36630,13 +36634,13 @@
         <v>2015</v>
       </c>
       <c r="F742" s="4" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="G742" s="1">
         <v>2015</v>
       </c>
       <c r="H742" s="4" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="I742" s="4" t="s">
         <v>16</v>
@@ -36674,13 +36678,13 @@
         <v>2015</v>
       </c>
       <c r="F743" s="4" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="G743" s="1">
         <v>2015</v>
       </c>
       <c r="H743" s="4" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I743" s="4" t="s">
         <v>16</v>
@@ -36718,13 +36722,13 @@
         <v>2015</v>
       </c>
       <c r="F744" s="4" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="G744" s="1">
         <v>2015</v>
       </c>
       <c r="H744" s="4" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I744" s="4" t="s">
         <v>16</v>
@@ -36762,13 +36766,13 @@
         <v>2015</v>
       </c>
       <c r="F745" s="4" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="G745" s="1">
         <v>2015</v>
       </c>
       <c r="H745" s="4" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="I745" s="4" t="s">
         <v>16</v>
@@ -36806,13 +36810,13 @@
         <v>2015</v>
       </c>
       <c r="F746" s="4" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="G746" s="1">
         <v>2015</v>
       </c>
       <c r="H746" s="4" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="I746" s="4" t="s">
         <v>16</v>
@@ -36850,13 +36854,13 @@
         <v>2015</v>
       </c>
       <c r="F747" s="4" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G747" s="1">
         <v>2015</v>
       </c>
       <c r="H747" s="4" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="I747" s="4" t="s">
         <v>16</v>
@@ -36894,13 +36898,13 @@
         <v>2015</v>
       </c>
       <c r="F748" s="4" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="G748" s="1">
         <v>2015</v>
       </c>
       <c r="H748" s="4" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="I748" s="4" t="s">
         <v>16</v>
@@ -36938,13 +36942,13 @@
         <v>2015</v>
       </c>
       <c r="F749" s="4" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G749" s="1">
         <v>2015</v>
       </c>
       <c r="H749" s="4" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="I749" s="4" t="s">
         <v>16</v>
@@ -36982,13 +36986,13 @@
         <v>2015</v>
       </c>
       <c r="F750" s="4" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="G750" s="1">
         <v>2015</v>
       </c>
       <c r="H750" s="4" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I750" s="4" t="s">
         <v>16</v>
@@ -37026,13 +37030,13 @@
         <v>2015</v>
       </c>
       <c r="F751" s="4" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="G751" s="1">
         <v>2015</v>
       </c>
       <c r="H751" s="4" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="I751" s="4" t="s">
         <v>16</v>
@@ -37070,13 +37074,13 @@
         <v>2015</v>
       </c>
       <c r="F752" s="4" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G752" s="1">
         <v>2015</v>
       </c>
       <c r="H752" s="4" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="I752" s="4" t="s">
         <v>16</v>
@@ -37114,13 +37118,13 @@
         <v>2015</v>
       </c>
       <c r="F753" s="4" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="G753" s="1">
         <v>2015</v>
       </c>
       <c r="H753" s="4" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="I753" s="4" t="s">
         <v>16</v>
@@ -37158,13 +37162,13 @@
         <v>2015</v>
       </c>
       <c r="F754" s="4" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="G754" s="1">
         <v>2015</v>
       </c>
       <c r="H754" s="4" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="I754" s="4" t="s">
         <v>16</v>
@@ -37202,13 +37206,13 @@
         <v>2015</v>
       </c>
       <c r="F755" s="4" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="G755" s="1">
         <v>2015</v>
       </c>
       <c r="H755" s="4" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="I755" s="4" t="s">
         <v>16</v>
@@ -37246,13 +37250,13 @@
         <v>2015</v>
       </c>
       <c r="F756" s="4" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="G756" s="1">
         <v>2015</v>
       </c>
       <c r="H756" s="4" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="I756" s="4" t="s">
         <v>16</v>
@@ -37290,13 +37294,13 @@
         <v>2015</v>
       </c>
       <c r="F757" s="4" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G757" s="1">
         <v>2015</v>
       </c>
       <c r="H757" s="4" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="I757" s="4" t="s">
         <v>16</v>
@@ -37334,13 +37338,13 @@
         <v>2015</v>
       </c>
       <c r="F758" s="4" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G758" s="1">
         <v>2015</v>
       </c>
       <c r="H758" s="4" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="I758" s="4" t="s">
         <v>16</v>
@@ -37378,13 +37382,13 @@
         <v>2015</v>
       </c>
       <c r="F759" s="4" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="G759" s="1">
         <v>2015</v>
       </c>
       <c r="H759" s="4" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="I759" s="4" t="s">
         <v>16</v>
@@ -37422,13 +37426,13 @@
         <v>2015</v>
       </c>
       <c r="F760" s="4" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="G760" s="1">
         <v>2015</v>
       </c>
       <c r="H760" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="I760" s="4" t="s">
         <v>16</v>
@@ -37466,13 +37470,13 @@
         <v>2015</v>
       </c>
       <c r="F761" s="4" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="G761" s="1">
         <v>2015</v>
       </c>
       <c r="H761" s="4" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="I761" s="4" t="s">
         <v>16</v>
@@ -37510,13 +37514,13 @@
         <v>2015</v>
       </c>
       <c r="F762" s="4" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="G762" s="1">
         <v>2015</v>
       </c>
       <c r="H762" s="4" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="I762" s="4" t="s">
         <v>16</v>
@@ -37554,13 +37558,13 @@
         <v>2015</v>
       </c>
       <c r="F763" s="4" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="G763" s="1">
         <v>2015</v>
       </c>
       <c r="H763" s="4" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="I763" s="4" t="s">
         <v>16</v>
@@ -37598,13 +37602,13 @@
         <v>2015</v>
       </c>
       <c r="F764" s="4" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="G764" s="1">
         <v>2015</v>
       </c>
       <c r="H764" s="4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="I764" s="4" t="s">
         <v>16</v>
@@ -37642,13 +37646,13 @@
         <v>2015</v>
       </c>
       <c r="F765" s="4" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="G765" s="1">
         <v>2015</v>
       </c>
       <c r="H765" s="4" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="I765" s="4" t="s">
         <v>16</v>
@@ -37686,13 +37690,13 @@
         <v>2015</v>
       </c>
       <c r="F766" s="4" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="G766" s="1">
         <v>2015</v>
       </c>
       <c r="H766" s="4" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="I766" s="4" t="s">
         <v>16</v>
@@ -37730,13 +37734,13 @@
         <v>2015</v>
       </c>
       <c r="F767" s="4" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G767" s="1">
         <v>2015</v>
       </c>
       <c r="H767" s="4" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="I767" s="4" t="s">
         <v>16</v>
@@ -37774,13 +37778,13 @@
         <v>2015</v>
       </c>
       <c r="F768" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="G768" s="1">
         <v>2015</v>
       </c>
       <c r="H768" s="4" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="I768" s="4" t="s">
         <v>16</v>
@@ -37818,13 +37822,13 @@
         <v>2015</v>
       </c>
       <c r="F769" s="4" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G769" s="1">
         <v>2015</v>
       </c>
       <c r="H769" s="4" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="I769" s="4" t="s">
         <v>16</v>
@@ -37862,19 +37866,19 @@
         <v>2015</v>
       </c>
       <c r="F770" s="4" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G770" s="1">
         <v>2015</v>
       </c>
       <c r="H770" s="4" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="I770" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J770" s="4" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="K770" s="1">
         <v>8090</v>
@@ -37904,19 +37908,19 @@
         <v>2015</v>
       </c>
       <c r="F771" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G771" s="1">
+        <v>2015</v>
+      </c>
+      <c r="H771" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="I771" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J771" s="4" t="s">
         <v>1204</v>
-      </c>
-      <c r="G771" s="1">
-        <v>2015</v>
-      </c>
-      <c r="H771" s="4" t="s">
-        <v>1205</v>
-      </c>
-      <c r="I771" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J771" s="4" t="s">
-        <v>1203</v>
       </c>
       <c r="K771" s="1">
         <v>8100</v>
@@ -37946,19 +37950,19 @@
         <v>2015</v>
       </c>
       <c r="F772" s="4" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="G772" s="1">
         <v>2015</v>
       </c>
       <c r="H772" s="4" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="I772" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J772" s="4" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="K772" s="1">
         <v>8110</v>
@@ -37988,19 +37992,19 @@
         <v>2015</v>
       </c>
       <c r="F773" s="4" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G773" s="1">
         <v>2015</v>
       </c>
       <c r="H773" s="4" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="I773" s="4" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="J773" s="4" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="K773" s="1">
         <v>8120</v>
